--- a/output/pdf_financials_xlsx/III.xlsx
+++ b/output/pdf_financials_xlsx/III.xlsx
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -22576,7 +22576,11 @@
           <t>Warrant Reserve 14 689</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -29354,7 +29358,11 @@
           <t>Warrant Reserve 13</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/III.xlsx
+++ b/output/pdf_financials_xlsx/III.xlsx
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-18.384</v>
+        <v>-18.62</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>44.537</v>
+        <v>43.957</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>84.55</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-37.285</v>
+        <v>-37.402</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-96.961</v>
+        <v>-97.086</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-57.275</v>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.577</v>
+        <v>-3.813</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>68.97799999999999</v>
+        <v>68.398</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>108.042</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-18.002</v>
+        <v>-18.119</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-64.57899999999999</v>
+        <v>-64.70399999999999</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>24.112</v>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1.778389853681819</v>
+        <v>-1.895722815792221</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>28.00898197514121</v>
+        <v>27.77346906456708</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>42.67482966327639</v>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-13.75153732745648</v>
+        <v>-13.84091238952249</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-50.17754329803187</v>
+        <v>-50.27466764050007</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>5.630776847306746</v>
@@ -2484,13 +2484,13 @@
         <v>23.854</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>28.818</v>
+        <v>23.854</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>34.475</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>12.364</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -2498,28 +2498,28 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>19.913</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>9.188000000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>14.251</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>51.895</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>18.574</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>89.953</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>33.308</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>27.541</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>24.936</v>
@@ -2604,13 +2604,13 @@
         <v>24.07</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>29.034</v>
+        <v>24.07</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>27.5</v>
+        <v>61.975</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>25</v>
+        <v>37.364</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
@@ -2618,28 +2618,28 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.321</v>
+        <v>20.234</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>9.273999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.123</v>
+        <v>14.374</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>2.27</v>
+        <v>54.165</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.325</v>
+        <v>19.899</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.039</v>
+        <v>89.992</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.081</v>
+        <v>33.389</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>27.541</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>24.936</v>
@@ -3324,13 +3324,13 @@
         <v>12.405</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.253</v>
+        <v>7.217</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>43.031</v>
+        <v>8.555999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>17.804</v>
+        <v>5.44</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
@@ -3341,25 +3341,25 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>11.35</v>
+        <v>2.162</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>17.124</v>
+        <v>2.873</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>55.774</v>
+        <v>3.879</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>25.24</v>
+        <v>6.666</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>92.92100000000001</v>
+        <v>2.968</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>36.911</v>
+        <v>3.603</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>32.684</v>
+        <v>5.143</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>5.688</v>
@@ -8063,25 +8063,25 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.053</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.468</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-2.467</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-3.644</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>-1.43</v>
+        <v>-5.287</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>-3.212</v>
+        <v>-9.035</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>-4.532</v>
+        <v>-12.218</v>
       </c>
     </row>
     <row r="125">
@@ -8123,25 +8123,25 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.053</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.468</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-2.467</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-3.644</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>-1.43</v>
+        <v>-5.287</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>-3.212</v>
+        <v>-9.035</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>-4.532</v>
+        <v>-12.218</v>
       </c>
     </row>
     <row r="126">
@@ -9626,7 +9626,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -12578,7 +12582,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -12883,7 +12887,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -32730,7 +32734,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -34647,7 +34651,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -38576,7 +38580,11 @@
           <t>Future Site Reclamation Deposits (Note 16)</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -41295,7 +41303,11 @@
           <t>Future Site Reclamation Deposits</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E326" s="5" t="n">
         <v>6.778</v>
       </c>
@@ -49076,7 +49088,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -51245,7 +51261,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -54573,7 +54593,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -65852,7 +65876,11 @@
           <t>Increase in future site reclamation deposits</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E575" s="5" t="n">
         <v>-1.713</v>
       </c>
@@ -66745,7 +66773,11 @@
           <t>Increase in future site reclamation deposits</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E584" t="inlineStr">
         <is>
           <t>-</t>
@@ -72946,7 +72978,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -73629,7 +73661,7 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -74777,7 +74809,7 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -78937,7 +78969,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -82735,7 +82767,7 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -83939,7 +83971,7 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
@@ -85143,7 +85175,7 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -88038,7 +88070,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
@@ -93743,7 +93775,7 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">

--- a/output/pdf_financials_xlsx/III.xlsx
+++ b/output/pdf_financials_xlsx/III.xlsx
@@ -1651,10 +1651,10 @@
         <v>77.113</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-125.595</v>
+        <v>-109.464</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>321.736</v>
+        <v>-40.266</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-26.07</v>
@@ -4561,10 +4561,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>16.238</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>19.348</v>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
@@ -4572,22 +4572,22 @@
         </is>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>30.277</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>35.832</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>46.702</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>41.736</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>50.38</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>34.294</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>0</v>
@@ -4621,10 +4621,10 @@
         <v>24.324</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>27.873</v>
+        <v>44.111</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>46.292</v>
+        <v>65.64</v>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
@@ -4632,22 +4632,22 @@
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>77.651</v>
+        <v>107.928</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>79.084</v>
+        <v>114.916</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>115.649</v>
+        <v>162.351</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>110.043</v>
+        <v>151.779</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>104.621</v>
+        <v>155.001</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>49.3</v>
+        <v>83.59399999999999</v>
       </c>
       <c r="N68" s="3" t="n">
         <v>59.582</v>
@@ -5041,10 +5041,10 @@
         <v>39.555</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>3.268</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>500.16</v>
+        <v>449.78</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>4.731</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>0.894</v>
@@ -6537,7 +6537,7 @@
         <v>-12.759</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>38.375</v>
+        <v>35.323</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>48.708</v>
@@ -6951,19 +6951,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>13.806</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-43.775</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-19.835</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>44.922</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-40.015</v>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>51.529</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-32.56</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>26.716</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-0.043</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>9.728</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>-1.009</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>6.183</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-26.626</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>-3.286</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>-20.388</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0</v>
+        <v>10.227</v>
       </c>
     </row>
     <row r="107">
@@ -7523,10 +7523,10 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>1.505</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>1.234</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -48130,7 +48130,11 @@
           <t>Net change in non-cash operating working capital balances 14</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -50689,7 +50693,11 @@
           <t>Net change in non-cash operating working capital balances 15</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -52912,7 +52920,11 @@
           <t>Net change in non-cash operating working capital balances 13</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -53801,7 +53813,11 @@
           <t>Net change in non-cash operating working capital balances 24</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -55484,7 +55500,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -56765,7 +56785,11 @@
           <t>Net change in non‐cash operating working capital balances 23</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -59577,7 +59601,11 @@
           <t>Net change in non‐cash operating working capital balances 21</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
@@ -61870,7 +61898,11 @@
           <t>Net change in non‐cash operating working capital balances 22</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
@@ -63759,7 +63791,11 @@
           <t>Net change in non‐cash operating working capital balances 20</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
@@ -65272,7 +65308,11 @@
           <t>Net change in non-cash operating working capital balances 19</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E569" t="inlineStr">
         <is>
           <t>-</t>
@@ -66573,7 +66613,11 @@
           <t>Net change in non cash operating working capital balances 21</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
@@ -67688,7 +67732,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E593" t="inlineStr">
         <is>
           <t>-</t>
@@ -67983,7 +68031,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E596" s="5" t="n">
         <v>21.125</v>
       </c>
@@ -68278,7 +68330,11 @@
           <t>Net change in non-cash operating working capital balances (Note 18)</t>
         </is>
       </c>
-      <c r="D599" t="inlineStr"/>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E599" t="inlineStr">
         <is>
           <t>-</t>
@@ -70064,7 +70120,11 @@
           <t>Net change in non-cash operating working capital balances (Note 19)</t>
         </is>
       </c>
-      <c r="D617" t="inlineStr"/>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E617" s="5" t="n">
         <v>13.806</v>
       </c>
@@ -79773,7 +79833,11 @@
           <t>Net Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E716" t="inlineStr">
         <is>
           <t>-</t>
